--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-indicacion-medicamento-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-indicacion-medicamento-urgencia.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/indicacion-medicamento-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/indicacion-medicamento-urgencia</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
 </t>
   </si>
   <si>
-    <t>Ordering of medication for patient or group</t>
+    <t>Medicamento indicado al alta de urgencia</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
@@ -611,7 +611,7 @@
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>Sistema de identificadores de indicaciones del establecimiento</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -638,7 +638,7 @@
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
+    <t>Identificador de la indicación</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -709,7 +709,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
+    <t>Estado de la indicación (active al alta)</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -766,7 +766,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
+    <t>order: indicación médica</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -887,7 +887,7 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t>Medication to be taken</t>
+    <t>Medicamento indicado</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -988,7 +988,7 @@
 </t>
   </si>
   <si>
-    <t>Who or group medication request is for</t>
+    <t>Paciente</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -1017,11 +1017,11 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/encuentro-urgencia)
+    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/encuentro-urgencia)
 </t>
   </si>
   <si>
-    <t>Encounter created as part of encounter/admission/stay</t>
+    <t>Episodio de urgencia en que se indica</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -1068,7 +1068,7 @@
 </t>
   </si>
   <si>
-    <t>When request was initially authored</t>
+    <t>Fecha y hora de la indicación</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1096,7 +1096,7 @@
 </t>
   </si>
   <si>
-    <t>Who/What requested the Request</t>
+    <t>Profesional que indica</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1362,7 +1362,7 @@
 </t>
   </si>
   <si>
-    <t>How the medication should be taken</t>
+    <t>Posología</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-indicacion-medicamento-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-indicacion-medicamento-urgencia.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$103</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3542" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3837" uniqueCount="713">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -333,13 +333,190 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest.implicitRules</t>
+    <t>MedicationRequest.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>R (restringido) si el episodio está restringido</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>MedicationRequest.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -435,28 +612,10 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -509,39 +668,7 @@
     <t>MedicationRequest.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.use</t>
@@ -593,9 +720,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -746,9 +870,6 @@
   </si>
   <si>
     <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled". The reason why the MedicationRequest was created at all is captured in reasonCode, not here.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Identifies the reasons for a given status.</t>
@@ -930,10 +1051,6 @@
   </si>
   <si>
     <t>MedicationRequest.medication[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -2430,7 +2547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO95"/>
+  <dimension ref="A1:AO103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.15234375" customWidth="true" bestFit="true"/>
@@ -2969,10 +3086,10 @@
         <v>81</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>104</v>
@@ -2983,9 +3100,7 @@
       <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>81</v>
@@ -3034,28 +3149,28 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL5" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM5" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM5" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>81</v>
@@ -3073,14 +3188,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -3092,16 +3207,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3127,43 +3242,43 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -3172,7 +3287,7 @@
         <v>81</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>81</v>
@@ -3183,14 +3298,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -3206,10 +3321,10 @@
         <v>81</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>121</v>
@@ -3289,7 +3404,7 @@
         <v>81</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>81</v>
@@ -3300,21 +3415,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>81</v>
@@ -3323,19 +3438,19 @@
         <v>81</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3385,19 +3500,19 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>81</v>
@@ -3406,7 +3521,7 @@
         <v>81</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>81</v>
@@ -3417,21 +3532,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>81</v>
@@ -3440,19 +3555,19 @@
         <v>81</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3502,19 +3617,19 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -3523,7 +3638,7 @@
         <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>81</v>
@@ -3534,14 +3649,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3554,26 +3669,24 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>81</v>
       </c>
@@ -3621,7 +3734,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3633,7 +3746,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3642,7 +3755,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -3653,10 +3766,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3664,7 +3777,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>80</v>
@@ -3676,19 +3789,19 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3714,13 +3827,13 @@
         <v>81</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>81</v>
@@ -3738,7 +3851,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3753,27 +3866,27 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3784,7 +3897,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>81</v>
@@ -3793,18 +3906,20 @@
         <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>81</v>
@@ -3829,13 +3944,13 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>81</v>
@@ -3853,19 +3968,19 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>81</v>
@@ -3874,7 +3989,7 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>81</v>
@@ -3885,42 +4000,42 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3958,31 +4073,31 @@
         <v>81</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>81</v>
@@ -3991,7 +4106,7 @@
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
@@ -4002,10 +4117,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4022,26 +4137,24 @@
         <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>81</v>
       </c>
@@ -4065,13 +4178,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4089,7 +4202,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -4110,25 +4223,25 @@
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4144,23 +4257,21 @@
         <v>81</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>81</v>
       </c>
@@ -4184,13 +4295,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4208,7 +4319,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4229,57 +4340,55 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>104</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>81</v>
       </c>
@@ -4291,7 +4400,7 @@
         <v>81</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>195</v>
+        <v>81</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>81</v>
@@ -4327,19 +4436,19 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
@@ -4348,53 +4457,53 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>198</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4408,7 +4517,7 @@
         <v>81</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>81</v>
@@ -4444,19 +4553,19 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
@@ -4465,53 +4574,57 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>208</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -4559,19 +4672,19 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4580,21 +4693,21 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>213</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4602,31 +4715,31 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4676,13 +4789,13 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
@@ -4691,27 +4804,27 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4719,32 +4832,30 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4769,13 +4880,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4793,10 +4904,10 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>107</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>90</v>
@@ -4805,19 +4916,19 @@
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>108</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4825,21 +4936,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -4851,16 +4962,16 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>113</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4886,52 +4997,52 @@
         <v>81</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>238</v>
+        <v>81</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>118</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4940,12 +5051,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4953,13 +5064,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>91</v>
@@ -4968,18 +5079,20 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
       </c>
@@ -4988,7 +5101,7 @@
         <v>81</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>81</v>
@@ -5003,13 +5116,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -5027,10 +5140,10 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>90</v>
@@ -5042,27 +5155,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5073,7 +5186,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -5082,21 +5195,23 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -5120,13 +5235,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>236</v>
+        <v>148</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -5144,13 +5259,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -5162,24 +5277,24 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>81</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5187,13 +5302,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>81</v>
@@ -5202,16 +5317,20 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -5223,7 +5342,7 @@
         <v>81</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>81</v>
@@ -5235,13 +5354,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -5259,7 +5378,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5274,27 +5393,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>81</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5302,31 +5421,31 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5340,7 +5459,7 @@
         <v>81</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>81</v>
@@ -5376,7 +5495,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5397,21 +5516,21 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5434,13 +5553,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5491,7 +5610,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5512,21 +5631,21 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5534,13 +5653,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>81</v>
@@ -5549,16 +5668,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5584,13 +5703,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>283</v>
+        <v>81</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5608,10 +5727,10 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>90</v>
@@ -5623,27 +5742,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>288</v>
+        <v>261</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5651,30 +5770,32 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>159</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5699,13 +5820,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5723,10 +5844,10 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>90</v>
@@ -5735,19 +5856,19 @@
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>271</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5755,21 +5876,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5781,16 +5902,16 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>137</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>139</v>
+        <v>275</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5816,52 +5937,52 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>162</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5870,12 +5991,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5883,35 +6004,33 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>292</v>
+        <v>166</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5920,7 +6039,7 @@
         <v>81</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>81</v>
@@ -5935,13 +6054,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>81</v>
+        <v>285</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5959,13 +6078,13 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
@@ -5974,27 +6093,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>81</v>
+        <v>287</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>299</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6002,35 +6121,33 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -6054,13 +6171,13 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -6078,13 +6195,13 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
@@ -6096,24 +6213,24 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6121,13 +6238,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>81</v>
@@ -6136,17 +6253,15 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>309</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -6171,13 +6286,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -6195,10 +6310,10 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>90</v>
@@ -6210,27 +6325,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6238,31 +6353,31 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6312,7 +6427,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6327,27 +6442,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6358,7 +6473,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -6367,16 +6482,16 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6427,13 +6542,13 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
@@ -6442,16 +6557,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6459,10 +6574,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6485,15 +6600,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>221</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6518,13 +6635,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>81</v>
+        <v>321</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6542,10 +6659,10 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>90</v>
@@ -6557,27 +6674,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>341</v>
+        <v>327</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6585,28 +6702,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>343</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>344</v>
+        <v>105</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>345</v>
+        <v>106</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6657,7 +6774,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>342</v>
+        <v>107</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6669,19 +6786,19 @@
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>315</v>
+        <v>108</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6689,21 +6806,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6715,15 +6832,17 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>349</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>350</v>
+        <v>112</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6760,43 +6879,43 @@
         <v>81</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>118</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>108</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6804,10 +6923,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6818,7 +6937,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6830,18 +6949,20 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6865,13 +6986,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>359</v>
+        <v>81</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6889,13 +7010,13 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
@@ -6904,27 +7025,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6932,31 +7053,35 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>364</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -7004,7 +7129,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7025,21 +7150,21 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>81</v>
+        <v>345</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7047,31 +7172,31 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>180</v>
+        <v>347</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7097,13 +7222,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>373</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7121,13 +7246,13 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
@@ -7136,27 +7261,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>379</v>
+        <v>355</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7164,13 +7289,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
@@ -7179,16 +7304,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7238,13 +7363,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -7253,27 +7378,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7293,16 +7418,16 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7353,7 +7478,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7368,27 +7493,27 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7396,13 +7521,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
@@ -7411,13 +7536,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>372</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7468,13 +7593,13 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
@@ -7483,27 +7608,27 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7511,13 +7636,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
@@ -7526,13 +7651,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7583,13 +7708,13 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
@@ -7598,27 +7723,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>401</v>
+        <v>353</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>81</v>
+        <v>385</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7632,27 +7757,25 @@
         <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>148</v>
+        <v>387</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7700,7 +7823,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7715,16 +7838,16 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7732,10 +7855,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7755,19 +7878,19 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7793,13 +7916,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7817,7 +7940,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7832,13 +7955,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>81</v>
+        <v>399</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7849,10 +7972,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7863,7 +7986,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7875,13 +7998,13 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7932,13 +8055,13 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -7947,16 +8070,16 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -7964,10 +8087,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7990,15 +8113,17 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>422</v>
+        <v>221</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8023,13 +8148,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -8047,7 +8172,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8062,27 +8187,27 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8090,13 +8215,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>81</v>
@@ -8105,16 +8230,16 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8164,7 +8289,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8179,16 +8304,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -8196,10 +8321,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8210,7 +8335,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -8219,16 +8344,16 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>158</v>
+        <v>426</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>159</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>160</v>
+        <v>428</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8279,28 +8404,28 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>161</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -8311,14 +8436,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8334,20 +8459,18 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>137</v>
+        <v>432</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8384,19 +8507,19 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>168</v>
+        <v>431</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8408,7 +8531,7 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
@@ -8417,7 +8540,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -8428,14 +8551,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8448,26 +8571,22 @@
         <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>136</v>
+        <v>435</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8515,7 +8634,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8527,16 +8646,16 @@
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>133</v>
+        <v>439</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8545,12 +8664,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8564,7 +8683,7 @@
         <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>81</v>
@@ -8573,17 +8692,17 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>443</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8632,7 +8751,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8647,27 +8766,27 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8675,33 +8794,33 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8725,13 +8844,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8749,7 +8868,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8770,21 +8889,21 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8804,23 +8923,19 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>180</v>
+        <v>454</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8844,13 +8959,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8868,7 +8983,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8883,27 +8998,27 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8914,7 +9029,7 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8923,16 +9038,16 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>158</v>
+        <v>460</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8983,13 +9098,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -8998,27 +9113,27 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9026,35 +9141,33 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L57" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>474</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -9102,13 +9215,13 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
@@ -9117,13 +9230,13 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -9134,10 +9247,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9157,20 +9270,18 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>478</v>
+        <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>479</v>
+        <v>105</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9195,13 +9306,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -9219,7 +9330,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>484</v>
+        <v>107</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9231,7 +9342,7 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -9240,32 +9351,32 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>485</v>
+        <v>108</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>486</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -9274,23 +9385,21 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>488</v>
+        <v>112</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>489</v>
+        <v>113</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9314,43 +9423,43 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>494</v>
+        <v>118</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9359,54 +9468,56 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>495</v>
+        <v>108</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>496</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>498</v>
+        <v>477</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>500</v>
+        <v>196</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9431,13 +9542,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9455,19 +9566,19 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
@@ -9476,21 +9587,21 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>504</v>
+        <v>189</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9513,19 +9624,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>180</v>
+        <v>481</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9550,13 +9659,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>511</v>
+        <v>81</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9574,7 +9683,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>485</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9595,21 +9704,21 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>514</v>
+        <v>486</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>515</v>
+        <v>487</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9617,13 +9726,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>81</v>
@@ -9632,16 +9741,18 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>517</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9689,13 +9800,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>520</v>
+        <v>492</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9710,21 +9821,21 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>521</v>
+        <v>493</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9735,7 +9846,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9744,19 +9855,23 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>159</v>
+        <v>495</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9780,13 +9895,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>81</v>
+        <v>499</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>81</v>
+        <v>500</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9804,19 +9919,19 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>161</v>
+        <v>501</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
@@ -9825,32 +9940,32 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>162</v>
+        <v>486</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9859,20 +9974,18 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>137</v>
+        <v>504</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9909,31 +10022,31 @@
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>168</v>
+        <v>506</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -9942,21 +10055,21 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>162</v>
+        <v>486</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9979,17 +10092,19 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>180</v>
+        <v>508</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10014,13 +10129,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>528</v>
+        <v>81</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>529</v>
+        <v>81</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -10038,7 +10153,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10059,21 +10174,21 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>81</v>
+        <v>514</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>531</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10096,20 +10211,18 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10133,13 +10246,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>81</v>
+        <v>520</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -10157,7 +10270,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10178,21 +10291,21 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>539</v>
+        <v>524</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10215,19 +10328,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>541</v>
+        <v>221</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10252,13 +10365,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>81</v>
+        <v>530</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>81</v>
+        <v>531</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10276,7 +10389,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10297,21 +10410,21 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>548</v>
+        <v>534</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10334,19 +10447,17 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>550</v>
+        <v>221</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10371,13 +10482,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>81</v>
+        <v>539</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10395,7 +10506,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10416,21 +10527,21 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10453,19 +10564,19 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>559</v>
+        <v>221</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10490,13 +10601,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>81</v>
+        <v>549</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>81</v>
+        <v>550</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10514,7 +10625,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10535,21 +10646,21 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>81</v>
+        <v>553</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10560,7 +10671,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -10572,18 +10683,16 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>569</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10631,13 +10740,13 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
@@ -10652,21 +10761,21 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>565</v>
+        <v>81</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>81</v>
+        <v>559</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10689,13 +10798,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>572</v>
+        <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>573</v>
+        <v>105</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>574</v>
+        <v>106</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10746,7 +10855,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>571</v>
+        <v>107</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10758,16 +10867,16 @@
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>576</v>
+        <v>108</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10778,21 +10887,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -10804,15 +10913,17 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10849,31 +10960,31 @@
         <v>81</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>81</v>
@@ -10882,7 +10993,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10893,21 +11004,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
@@ -10916,21 +11027,21 @@
         <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>137</v>
+        <v>563</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10954,13 +11065,13 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>81</v>
+        <v>566</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>81</v>
+        <v>567</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -10978,19 +11089,19 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>168</v>
+        <v>568</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>81</v>
@@ -10999,56 +11110,56 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>136</v>
+        <v>571</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>439</v>
+        <v>572</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>440</v>
+        <v>573</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>139</v>
+        <v>574</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>145</v>
+        <v>575</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11097,19 +11208,19 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>441</v>
+        <v>576</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>81</v>
@@ -11118,21 +11229,21 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>133</v>
+        <v>552</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>81</v>
+        <v>577</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11152,21 +11263,23 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
       </c>
@@ -11214,7 +11327,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11235,21 +11348,21 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>81</v>
+        <v>586</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11269,19 +11382,23 @@
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>158</v>
+        <v>588</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>159</v>
+        <v>589</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>592</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11329,7 +11446,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>161</v>
+        <v>593</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11341,7 +11458,7 @@
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
@@ -11350,32 +11467,32 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>162</v>
+        <v>594</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>81</v>
+        <v>595</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
@@ -11384,21 +11501,23 @@
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>136</v>
+        <v>597</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>137</v>
+        <v>598</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>164</v>
+        <v>599</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11446,19 +11565,19 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>168</v>
+        <v>602</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>81</v>
@@ -11467,7 +11586,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>162</v>
+        <v>603</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11478,45 +11597,43 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>136</v>
+        <v>597</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>439</v>
+        <v>605</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>145</v>
+        <v>607</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11565,19 +11682,19 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>441</v>
+        <v>608</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>81</v>
@@ -11586,7 +11703,7 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>133</v>
+        <v>603</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -11597,10 +11714,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11623,13 +11740,13 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>559</v>
+        <v>610</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>589</v>
+        <v>611</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>590</v>
+        <v>612</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11680,7 +11797,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11698,10 +11815,10 @@
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>81</v>
+        <v>613</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -11712,10 +11829,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11738,13 +11855,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>593</v>
+        <v>104</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>594</v>
+        <v>105</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>595</v>
+        <v>106</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11795,7 +11912,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>592</v>
+        <v>107</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11807,7 +11924,7 @@
         <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>81</v>
@@ -11816,7 +11933,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>596</v>
+        <v>108</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11827,21 +11944,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
@@ -11853,15 +11970,17 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>593</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>598</v>
+        <v>112</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -11910,19 +12029,19 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>597</v>
+        <v>118</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>81</v>
@@ -11931,7 +12050,7 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>596</v>
+        <v>108</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -11942,45 +12061,45 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>208</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>601</v>
+        <v>477</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>602</v>
+        <v>478</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>603</v>
+        <v>114</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>604</v>
+        <v>196</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12029,28 +12148,28 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>600</v>
+        <v>479</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>605</v>
+        <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>606</v>
+        <v>189</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12061,10 +12180,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12087,16 +12206,16 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12146,7 +12265,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12164,24 +12283,24 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>612</v>
+        <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>614</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12204,13 +12323,13 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>559</v>
+        <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>616</v>
+        <v>105</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>617</v>
+        <v>106</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12261,7 +12380,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>615</v>
+        <v>107</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12273,41 +12392,41 @@
         <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>618</v>
+        <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>619</v>
+        <v>108</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>620</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12319,16 +12438,16 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>593</v>
+        <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>622</v>
+        <v>112</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>623</v>
+        <v>113</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>624</v>
+        <v>114</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12378,28 +12497,28 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>621</v>
+        <v>118</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>625</v>
+        <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>626</v>
+        <v>108</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -12410,42 +12529,46 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>628</v>
+        <v>477</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12493,19 +12616,19 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>627</v>
+        <v>479</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
@@ -12514,10 +12637,10 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>630</v>
+        <v>189</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>81</v>
@@ -12525,10 +12648,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12551,13 +12674,13 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12608,7 +12731,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12626,10 +12749,10 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>634</v>
+        <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -12640,10 +12763,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12666,13 +12789,13 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>158</v>
+        <v>631</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>159</v>
+        <v>632</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>160</v>
+        <v>633</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12723,7 +12846,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>161</v>
+        <v>630</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12735,7 +12858,7 @@
         <v>81</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>81</v>
@@ -12744,7 +12867,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>162</v>
+        <v>634</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -12755,21 +12878,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>81</v>
@@ -12781,17 +12904,15 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>136</v>
+        <v>631</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>137</v>
+        <v>636</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12840,19 +12961,19 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>168</v>
+        <v>635</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>81</v>
@@ -12861,7 +12982,7 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>162</v>
+        <v>634</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12879,38 +13000,38 @@
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>136</v>
+        <v>248</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>439</v>
+        <v>639</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>440</v>
+        <v>640</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>139</v>
+        <v>641</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>145</v>
+        <v>642</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -12959,28 +13080,28 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>441</v>
+        <v>638</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>81</v>
+        <v>643</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>133</v>
+        <v>644</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -12991,10 +13112,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13002,7 +13123,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>90</v>
@@ -13017,16 +13138,16 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>478</v>
+        <v>646</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13052,13 +13173,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>643</v>
+        <v>81</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>644</v>
+        <v>81</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -13076,10 +13197,10 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>90</v>
@@ -13094,24 +13215,24 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13134,13 +13255,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>180</v>
+        <v>597</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13167,13 +13288,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>650</v>
+        <v>81</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -13191,7 +13312,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13209,24 +13330,24 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13249,15 +13370,17 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>656</v>
+        <v>631</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>662</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -13306,7 +13429,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13321,13 +13444,13 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>659</v>
+        <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
@@ -13338,21 +13461,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>662</v>
+        <v>81</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
@@ -13364,17 +13487,15 @@
         <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>663</v>
+        <v>255</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>666</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13423,13 +13544,13 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>81</v>
@@ -13444,10 +13565,10 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13455,10 +13576,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13469,7 +13590,7 @@
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
@@ -13481,7 +13602,7 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>669</v>
+        <v>610</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>670</v>
@@ -13489,9 +13610,7 @@
       <c r="M95" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>672</v>
-      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13540,13 +13659,13 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>81</v>
@@ -13555,23 +13674,955 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="AL95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="AN95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO95" t="s" s="2">
+      <c r="B96" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO103" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO95">
+  <autoFilter ref="A1:AO103">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13581,7 +14632,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI94">
+  <conditionalFormatting sqref="A2:AI102">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
